--- a/docs/S1/dedication/7-S1-dedication.xlsx
+++ b/docs/S1/dedication/7-S1-dedication.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uses0-my.sharepoint.com/personal/celsuacor_alum_us_es/Documents/ISPP/Docs Proyecto/1. S1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{FE392467-8A49-4D14-92BC-52BF3AF17752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A7C8D4D-9086-48A3-83F2-4BC991D0040C}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{FE392467-8A49-4D14-92BC-52BF3AF17752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E14A703-6A6B-4113-A8AE-7C6CCD8C1F00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02C8C9D8-2F21-45BA-9A66-91BB45160C54}"/>
   </bookViews>
@@ -827,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -964,7 +964,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -1049,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -1100,7 +1100,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D25" s="5">
         <f>SUM(D2:D22)/$B$24</f>
-        <v>0.9776190476190475</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5">
         <f>SUM(E2:E22)/$B$24</f>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="D26" s="6">
         <f t="shared" ref="D26:G26" si="0">1-D25</f>
-        <v>2.2380952380952501E-2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6">
         <f t="shared" si="0"/>
@@ -1532,14 +1532,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1a6abb52-502d-48a4-9af4-2c760790d608" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1548,14 +1540,22 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1a6abb52-502d-48a4-9af4-2c760790d608" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86F6973B-E301-4E76-B65C-A7477A18457B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0D844A-E87E-42E2-B155-132CABE67861}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0D844A-E87E-42E2-B155-132CABE67861}"/>
 </file>